--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:43</t>
+    <t xml:space="preserve">2026-09-09 20:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:04</t>
+    <t xml:space="preserve">2026-09-18 17:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_maule.xlsx
@@ -30,96 +30,96 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curepto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelluhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualañé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Clemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colbún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Javier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alegre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maule</t>
   </si>
   <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alegre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Javier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colbún</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Clemente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelluhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curepto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pencahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:04</t>
+    <t xml:space="preserve">2026-09-27 21:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -549,13 +549,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>47469</v>
+        <v>10184</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>62394</v>
+        <v>9171</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>76.08</v>
+        <v>111.05</v>
       </c>
     </row>
     <row r="3">
@@ -563,13 +563,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3781</v>
+        <v>11038</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4196</v>
+        <v>10078</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>90.11</v>
+        <v>109.53</v>
       </c>
     </row>
     <row r="4">
@@ -577,13 +577,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>17894</v>
+        <v>9378</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>19366</v>
+        <v>8614</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>92.4</v>
+        <v>108.87</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46641</v>
+        <v>10182</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>50413</v>
+        <v>9353</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>92.52</v>
+        <v>108.86</v>
       </c>
     </row>
     <row r="6">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>16336</v>
+        <v>8732</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>17656</v>
+        <v>8187</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>92.52</v>
+        <v>106.66</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>10546</v>
+        <v>17171</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11384</v>
+        <v>16370</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>92.64</v>
+        <v>104.89</v>
       </c>
     </row>
     <row r="8">
@@ -633,13 +633,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>29229</v>
+        <v>10488</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>31132</v>
+        <v>10232</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>93.89</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="9">
@@ -647,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>47630</v>
+        <v>44726</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>49994</v>
+        <v>44253</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>95.27</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="10">
@@ -661,13 +661,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>227720</v>
+        <v>6986</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>238343</v>
+        <v>6993</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>95.54</v>
+        <v>99.9</v>
       </c>
     </row>
     <row r="11">
@@ -675,13 +675,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>14301</v>
+        <v>101408</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>14859</v>
+        <v>101895</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>96.24</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="12">
@@ -689,13 +689,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>22015</v>
+        <v>4343</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>22813</v>
+        <v>4365</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>96.5</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="13">
@@ -703,13 +703,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>20463</v>
+        <v>44569</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>21194</v>
+        <v>44844</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>96.55</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="14">
@@ -717,13 +717,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>18902</v>
+        <v>162867</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>19556</v>
+        <v>165757</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>96.66</v>
+        <v>98.26</v>
       </c>
     </row>
     <row r="15">
@@ -731,13 +731,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45331</v>
+        <v>49170</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46751</v>
+        <v>50479</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>96.96</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="16">
@@ -745,13 +745,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9046</v>
+        <v>32093</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>9319</v>
+        <v>33051</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>97.07</v>
+        <v>97.1</v>
       </c>
     </row>
     <row r="17">
@@ -759,13 +759,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32093</v>
+        <v>9046</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>33051</v>
+        <v>9319</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>97.1</v>
+        <v>97.07</v>
       </c>
     </row>
     <row r="18">
@@ -773,13 +773,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>49170</v>
+        <v>45331</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>50479</v>
+        <v>46751</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>97.41</v>
+        <v>96.96</v>
       </c>
     </row>
     <row r="19">
@@ -787,13 +787,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>162867</v>
+        <v>18902</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>165757</v>
+        <v>19556</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>98.26</v>
+        <v>96.66</v>
       </c>
     </row>
     <row r="20">
@@ -801,13 +801,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>44569</v>
+        <v>20463</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>44844</v>
+        <v>21194</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>99.39</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="21">
@@ -815,13 +815,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4343</v>
+        <v>22015</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4365</v>
+        <v>22813</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>99.5</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="22">
@@ -829,13 +829,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>101408</v>
+        <v>14301</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>101895</v>
+        <v>14859</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>99.52</v>
+        <v>96.24</v>
       </c>
     </row>
     <row r="23">
@@ -843,13 +843,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>6986</v>
+        <v>227720</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6993</v>
+        <v>238343</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>99.9</v>
+        <v>95.54</v>
       </c>
     </row>
     <row r="24">
@@ -857,13 +857,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>44726</v>
+        <v>47630</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>44253</v>
+        <v>49994</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>101.07</v>
+        <v>95.27</v>
       </c>
     </row>
     <row r="25">
@@ -871,13 +871,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>10488</v>
+        <v>29229</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>10232</v>
+        <v>31132</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>102.5</v>
+        <v>93.89</v>
       </c>
     </row>
     <row r="26">
@@ -885,13 +885,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>17171</v>
+        <v>10546</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>16370</v>
+        <v>11384</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>104.89</v>
+        <v>92.64</v>
       </c>
     </row>
     <row r="27">
@@ -899,13 +899,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>8732</v>
+        <v>16336</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8187</v>
+        <v>17656</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>106.66</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="28">
@@ -913,13 +913,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10182</v>
+        <v>46641</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>9353</v>
+        <v>50413</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>108.86</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="29">
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>9378</v>
+        <v>17894</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>8614</v>
+        <v>19366</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>108.87</v>
+        <v>92.4</v>
       </c>
     </row>
     <row r="30">
@@ -941,13 +941,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>11038</v>
+        <v>3781</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>10078</v>
+        <v>4196</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>109.53</v>
+        <v>90.11</v>
       </c>
     </row>
     <row r="31">
@@ -955,13 +955,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>10184</v>
+        <v>47469</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>9171</v>
+        <v>62394</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>111.05</v>
+        <v>76.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:49</t>
+    <t xml:space="preserve">2026-10-05 05:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
